--- a/assets/DCS_Pattern.xlsx
+++ b/assets/DCS_Pattern.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://earthboundtradingcom-my.sharepoint.com/personal/wesley_earthboundtrading_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wesley\Documents\WebOrderAI\weborder-ai\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47865A7B-786B-4040-84AB-1E4915C98A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EACAE0FF-9549-4B6F-B385-E8376B684678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3ADF0970-51AE-460E-9CC1-C99EA7AA7C11}"/>
   </bookViews>
@@ -234,14 +234,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
@@ -254,8 +246,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -264,18 +263,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF3300"/>
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="0"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -285,45 +278,30 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="8"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color indexed="8"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color indexed="8"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="22"/>
-      </left>
-      <right style="thin">
-        <color indexed="22"/>
-      </right>
-      <top style="thin">
-        <color indexed="22"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="22"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -661,9 +639,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45C93F6B-1F07-471E-9688-8A286E2B98BD}">
-  <sheetPr>
-    <tabColor rgb="FFFF3300"/>
-  </sheetPr>
   <dimension ref="A1:B48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -672,386 +647,386 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>52</v>
       </c>
     </row>

--- a/assets/DCS_Pattern.xlsx
+++ b/assets/DCS_Pattern.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wesley\Documents\WebOrderAI\weborder-ai\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EACAE0FF-9549-4B6F-B385-E8376B684678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD970593-19BC-41C9-B0B0-3532A9A5B022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3ADF0970-51AE-460E-9CC1-C99EA7AA7C11}"/>
   </bookViews>
@@ -50,15 +50,9 @@
     <t>AC RB</t>
   </si>
   <si>
-    <t>Pattern 01</t>
-  </si>
-  <si>
     <t>AC BA</t>
   </si>
   <si>
-    <t>Pattern 02</t>
-  </si>
-  <si>
     <t>AC HA</t>
   </si>
   <si>
@@ -77,9 +71,6 @@
     <t>AS BT MI</t>
   </si>
   <si>
-    <t>Pattern 03</t>
-  </si>
-  <si>
     <t>AS CA</t>
   </si>
   <si>
@@ -89,9 +80,6 @@
     <t>AS IB</t>
   </si>
   <si>
-    <t>Pattern 04</t>
-  </si>
-  <si>
     <t>AS IN MI</t>
   </si>
   <si>
@@ -101,18 +89,12 @@
     <t>AS OB</t>
   </si>
   <si>
-    <t>Pattern 05</t>
-  </si>
-  <si>
     <t>AS OI</t>
   </si>
   <si>
     <t>CL ME OW</t>
   </si>
   <si>
-    <t>Pattern 06</t>
-  </si>
-  <si>
     <t>CL ME PA</t>
   </si>
   <si>
@@ -149,9 +131,6 @@
     <t>HD DO CD</t>
   </si>
   <si>
-    <t>Pattern 07</t>
-  </si>
-  <si>
     <t>HD DO DA</t>
   </si>
   <si>
@@ -170,36 +149,24 @@
     <t>HD TP</t>
   </si>
   <si>
-    <t>Pattern 08</t>
-  </si>
-  <si>
     <t>HD TX</t>
   </si>
   <si>
     <t>HD WD AC</t>
   </si>
   <si>
-    <t>Pattern 09</t>
-  </si>
-  <si>
     <t>HD WD BF</t>
   </si>
   <si>
     <t>IM BK</t>
   </si>
   <si>
-    <t>Pattern 10</t>
-  </si>
-  <si>
     <t>IM GF</t>
   </si>
   <si>
     <t>JE ME BR</t>
   </si>
   <si>
-    <t>Pattern 11</t>
-  </si>
-  <si>
     <t>JE ME NK</t>
   </si>
   <si>
@@ -219,6 +186,39 @@
   </si>
   <si>
     <t>JE WO RI</t>
+  </si>
+  <si>
+    <t>Pattern01</t>
+  </si>
+  <si>
+    <t>Pattern02</t>
+  </si>
+  <si>
+    <t>Pattern04</t>
+  </si>
+  <si>
+    <t>Pattern05</t>
+  </si>
+  <si>
+    <t>Pattern06</t>
+  </si>
+  <si>
+    <t>Pattern07</t>
+  </si>
+  <si>
+    <t>Pattern08</t>
+  </si>
+  <si>
+    <t>Pattern09</t>
+  </si>
+  <si>
+    <t>Pattern10</t>
+  </si>
+  <si>
+    <t>Pattern11</t>
+  </si>
+  <si>
+    <t>Pattern12</t>
   </si>
 </sst>
 </file>
@@ -298,7 +298,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -659,375 +659,375 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
